--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AZ\elec\MPCbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9C12A92-045D-4F7A-B390-267103D0ACD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C63E8CB7-3B84-4230-B540-5C3D886AE5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="1725" windowWidth="18645" windowHeight="9765" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1575" windowWidth="15870" windowHeight="16425" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Data" sheetId="2" r:id="rId11"/>
     <sheet name="MPCbS" sheetId="3" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1715,7 +1715,7 @@
         <v>105</v>
       </c>
       <c r="C1" s="24">
-        <v>45301</v>
+        <v>45348</v>
       </c>
       <c r="H1" s="25" t="s">
         <v>100</v>
@@ -5633,8 +5633,7 @@
         <v>57</v>
       </c>
       <c r="B16" s="14">
-        <f>B12</f>
-        <v>9000000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5660,7 +5659,7 @@
         <v>92</v>
       </c>
       <c r="B19" s="14">
-        <f>9*10^12</f>
+        <f>B2</f>
         <v>9000000000000</v>
       </c>
     </row>
@@ -5687,7 +5686,7 @@
         <v>95</v>
       </c>
       <c r="B22" s="14">
-        <f>IF(INDEX('coal ban'!D:D,MATCH(About!$B$2,'coal ban'!C:C,0))="yes",0,9*10^12)</f>
+        <f>B2</f>
         <v>9000000000000</v>
       </c>
     </row>
@@ -5946,7 +5945,7 @@
         <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -6144,7 +6143,7 @@
         <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
